--- a/inst/ars-examples/params_dm_ae.xlsx
+++ b/inst/ars-examples/params_dm_ae.xlsx
@@ -490,7 +490,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -632,7 +632,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Age group, n (%)</t>
+          <t>Age group 1, n (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sex, n (%)</t>
+          <t>Age group 2, n (%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TRT01A, SEX</t>
+          <t>TRT01A, AGEGR2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Race, n (%)</t>
+          <t>Sex, n (%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TRT01A, RACE</t>
+          <t>TRT01A, SEX</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Out_ae</t>
+          <t>Out_dm</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Number of subjects</t>
+          <t>Race, n (%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>total_n</t>
+          <t>categorical_summary</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -774,13 +774,23 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TRT01A, RACE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Out_ae</t>
+          <t>Out_dm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -790,7 +800,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Subjects with at least one TEAE, n (%)</t>
+          <t>Ethnicity, n (%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -800,7 +810,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ADAE</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -810,12 +820,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>TRTEMFL EQ Y</t>
+          <t>TRT01A, ETHNIC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -837,37 +842,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TEAE by System Organ Class, n (%)</t>
+          <t>Number of subjects</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>categorical_summary</t>
+          <t>total_n</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ADAE</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>TRT01A, ADAE.AEBODSYS</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>TRTEMFL EQ Y</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>auto</t>
         </is>
       </c>
     </row>
@@ -884,7 +874,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TEAE by Preferred Term, n (%)</t>
+          <t>Subjects with at least one TEAE, n (%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +894,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TRT01A, ADAE.AEDECOD</t>
+          <t>TRT01A</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -931,35 +921,129 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>TEAE by System Organ Class, n (%)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>categorical_summary</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TRT01A, ADAE.AEBODSYS</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TRTEMFL EQ Y</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Out_ae</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>An_11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TEAE by Preferred Term, n (%)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>categorical_summary</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TRT01A, ADAE.AEDECOD</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>TRTEMFL EQ Y</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Out_ae</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>An_12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>TEAE by severity, n (%)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>categorical_summary</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>ADAE</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>TRT01A, ADAE.AESEV</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>TRTEMFL EQ Y</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
